--- a/astro-site/public/dl/hotel-checklist-templates/01-hotel-breakfast-buffet-checklists.xlsx
+++ b/astro-site/public/dl/hotel-checklist-templates/01-hotel-breakfast-buffet-checklists.xlsx
@@ -1321,7 +1321,7 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>Set up the hot station: chafing dishes, pans, serving spoons</t>
+          <t>Set up the hot station: chafing dishes, pans and serving spoons, behind the sneeze guard (FDA 3-306.11)</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>Keep the buffet clean at all times: wipe up spills immediately</t>
+          <t>Keep the buffet watched by trained staff and clean at all times (FDA 3-306.13): wipe up spills immediately</t>
         </is>
       </c>
       <c r="C48" s="16" t="inlineStr">
